--- a/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.15007170680316</v>
+        <v>45.41862731346671</v>
       </c>
       <c r="M2" t="n">
-        <v>101.0191696675212</v>
+        <v>99.90566039343142</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08020997488649</v>
+        <v>88.02520265101752</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93553178628663</v>
+        <v>45.93520242356725</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228861054580284</v>
+        <v>2.228720267933066</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713217589048966</v>
+        <v>5.709922926368889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429536848600947</v>
+        <v>0.7429067559776886</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97493342979773</v>
+        <v>33.97541532180885</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17586950356435</v>
+        <v>34.17371077497367</v>
       </c>
       <c r="I3" t="n">
-        <v>6.600914182659468</v>
+        <v>6.551359379094811</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643460530375592</v>
+        <v>4.643167224860553</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91979002511351</v>
+        <v>11.97479734898246</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90775308574179</v>
+        <v>48.8548389297906</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630748971419</v>
+        <v>106.7648387023403</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26609409712391</v>
+        <v>87.13943999577191</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76264351700498</v>
+        <v>42.68111364171715</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190173793037029</v>
+        <v>2.186186739716586</v>
       </c>
       <c r="E4" t="n">
-        <v>6.53277492151147</v>
+        <v>6.51276840354611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445180252717429</v>
+        <v>0.7444614910513473</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38521648319301</v>
+        <v>33.32701888235935</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24782916250017</v>
+        <v>34.24522858836197</v>
       </c>
       <c r="I4" t="n">
-        <v>5.512344053662102</v>
+        <v>5.470891571665632</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653237657948393</v>
+        <v>4.652884319070919</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73390590287609</v>
+        <v>12.86056000422809</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32009185282283</v>
+        <v>44.2763441490799</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8166412727039</v>
+        <v>99.81801779502514</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22348192348606</v>
+        <v>85.97274562959811</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57567439016182</v>
+        <v>42.36358720211982</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139744243696562</v>
+        <v>2.129259194042513</v>
       </c>
       <c r="E5" t="n">
-        <v>7.149320761857313</v>
+        <v>7.104369736893408</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458425357748016</v>
+        <v>0.745779764197223</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61650971333127</v>
+        <v>32.45919485107272</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30875664564087</v>
+        <v>34.30586915307225</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601792174592735</v>
+        <v>4.567149404087351</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66151584859251</v>
+        <v>4.661123526232643</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77651807651393</v>
+        <v>14.02725437040189</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49468686516698</v>
+        <v>43.45718921715425</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84687933184273</v>
+        <v>99.84803078967596</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.9556141840601</v>
+        <v>84.60204561357082</v>
       </c>
       <c r="C6" t="n">
-        <v>42.02268731726075</v>
+        <v>41.7022298363018</v>
       </c>
       <c r="D6" t="n">
-        <v>2.078132377077886</v>
+        <v>2.062349927759335</v>
       </c>
       <c r="E6" t="n">
-        <v>7.583563906129601</v>
+        <v>7.516402880200666</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469664508925876</v>
+        <v>0.7468997800907236</v>
       </c>
       <c r="G6" t="n">
-        <v>31.67734885242723</v>
+        <v>31.43920587194583</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36045674105902</v>
+        <v>34.35738988417327</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8406055383951</v>
+        <v>3.81167364383397</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668540318078672</v>
+        <v>4.668123625567021</v>
       </c>
       <c r="K6" t="n">
-        <v>15.0443858159399</v>
+        <v>15.3979543864292</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80509930639399</v>
+        <v>42.77295051604435</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87217243959464</v>
+        <v>99.87313473877533</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.4667525219291</v>
+        <v>83.02760918428663</v>
       </c>
       <c r="C7" t="n">
-        <v>41.13056736028452</v>
+        <v>40.71982114791155</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00585042092441</v>
+        <v>1.985720795395159</v>
       </c>
       <c r="E7" t="n">
-        <v>7.853891186759632</v>
+        <v>7.767196832139536</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479224120225226</v>
+        <v>0.7478534700035221</v>
       </c>
       <c r="G7" t="n">
-        <v>30.57554188090546</v>
+        <v>30.27104374981586</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40443095303603</v>
+        <v>34.40125962016201</v>
       </c>
       <c r="I7" t="n">
-        <v>3.20460059314027</v>
+        <v>3.180450529248553</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674515075140765</v>
+        <v>4.674084187522012</v>
       </c>
       <c r="K7" t="n">
-        <v>16.5332474780709</v>
+        <v>16.97239081571336</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22950167446695</v>
+        <v>42.20190821293527</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89331651282237</v>
+        <v>99.89412017656016</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.09611288273489</v>
+        <v>88.0247627088464</v>
       </c>
       <c r="C8" t="n">
-        <v>43.31684252202817</v>
+        <v>43.08189100247805</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01004595364875</v>
+        <v>1.989999788993635</v>
       </c>
       <c r="E8" t="n">
-        <v>9.602828462104792</v>
+        <v>9.643441885605386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494868023290849</v>
+        <v>0.7494650058338184</v>
       </c>
       <c r="G8" t="n">
-        <v>31.04508488456175</v>
+        <v>30.79182070480223</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4763929071379</v>
+        <v>34.47539026835563</v>
       </c>
       <c r="I8" t="n">
-        <v>5.527981358395851</v>
+        <v>5.69048876879432</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68429251455678</v>
+        <v>4.684156286461363</v>
       </c>
       <c r="K8" t="n">
-        <v>11.90388711726509</v>
+        <v>11.97523729115361</v>
       </c>
       <c r="L8" t="n">
-        <v>44.59538893062512</v>
+        <v>44.75359661286239</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81611856991839</v>
+        <v>99.81072490649406</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.01008380876743</v>
+        <v>86.10264786495712</v>
       </c>
       <c r="C9" t="n">
-        <v>42.08919221734298</v>
+        <v>42.04295820367835</v>
       </c>
       <c r="D9" t="n">
-        <v>1.915171304142571</v>
+        <v>1.90333523519946</v>
       </c>
       <c r="E9" t="n">
-        <v>9.918721023451971</v>
+        <v>10.01526895108955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508272650272581</v>
+        <v>0.7508434206801451</v>
       </c>
       <c r="G9" t="n">
-        <v>29.57974945679915</v>
+        <v>29.45083593854683</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53805419125386</v>
+        <v>34.53879735128666</v>
       </c>
       <c r="I9" t="n">
-        <v>4.614890161672247</v>
+        <v>4.750795588903573</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692670406420361</v>
+        <v>4.692771379250905</v>
       </c>
       <c r="K9" t="n">
-        <v>13.98991619123258</v>
+        <v>13.89735213504288</v>
       </c>
       <c r="L9" t="n">
-        <v>43.76733655369122</v>
+        <v>43.90162052881226</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84644496226677</v>
+        <v>99.84193086753349</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.79281803934083</v>
+        <v>83.88796224709733</v>
       </c>
       <c r="C10" t="n">
-        <v>40.58816024689327</v>
+        <v>40.56543064833728</v>
       </c>
       <c r="D10" t="n">
-        <v>1.815411313301097</v>
+        <v>1.804279806116059</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04400053150737</v>
+        <v>10.15491585950558</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519776866229781</v>
+        <v>0.752026454928415</v>
       </c>
       <c r="G10" t="n">
-        <v>28.03896011408053</v>
+        <v>27.91812370960946</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59097358465699</v>
+        <v>34.59321692670707</v>
       </c>
       <c r="I10" t="n">
-        <v>3.851634267778236</v>
+        <v>3.965234146928157</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699860541393612</v>
+        <v>4.700165343302592</v>
       </c>
       <c r="K10" t="n">
-        <v>16.20718196065918</v>
+        <v>16.11203775290263</v>
       </c>
       <c r="L10" t="n">
-        <v>43.07646639906776</v>
+        <v>43.19056505462388</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87180860662022</v>
+        <v>99.86803345586381</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.48323174118362</v>
+        <v>81.51611687795878</v>
       </c>
       <c r="C11" t="n">
-        <v>38.87571255121287</v>
+        <v>38.80822742587208</v>
       </c>
       <c r="D11" t="n">
-        <v>1.712571744420533</v>
+        <v>1.699259905821299</v>
       </c>
       <c r="E11" t="n">
-        <v>10.01067969724628</v>
+        <v>10.11531100333093</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529663532298002</v>
+        <v>0.7530439754848447</v>
       </c>
       <c r="G11" t="n">
-        <v>26.45060680325531</v>
+        <v>26.29312155724853</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6364522485708</v>
+        <v>34.64002287230284</v>
       </c>
       <c r="I11" t="n">
-        <v>3.21391518677465</v>
+        <v>3.308832716990069</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70603970768625</v>
+        <v>4.706524846780278</v>
       </c>
       <c r="K11" t="n">
-        <v>18.51676825881639</v>
+        <v>18.48388312204121</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50052934919913</v>
+        <v>42.59774405911647</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89301015922838</v>
+        <v>99.88985460702976</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.14928357591684</v>
+        <v>79.15803378637759</v>
       </c>
       <c r="C12" t="n">
-        <v>37.03925354215942</v>
+        <v>36.96221344988633</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609680795369251</v>
+        <v>1.5959637419158</v>
       </c>
       <c r="E12" t="n">
-        <v>9.856121336459507</v>
+        <v>9.960506559445522</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538166110326592</v>
+        <v>0.7539193667564328</v>
       </c>
       <c r="G12" t="n">
-        <v>24.86145992760713</v>
+        <v>24.69479125788679</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67556410750231</v>
+        <v>34.68029087079589</v>
       </c>
       <c r="I12" t="n">
-        <v>2.681286978991864</v>
+        <v>2.760565947349428</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711353818954118</v>
+        <v>4.711996042227704</v>
       </c>
       <c r="K12" t="n">
-        <v>20.85071642408315</v>
+        <v>20.84196621362242</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02075461190259</v>
+        <v>42.10390831657484</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91072457814516</v>
+        <v>99.90808798008361</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.64305483256841</v>
+        <v>76.72834482990901</v>
       </c>
       <c r="C13" t="n">
-        <v>34.94725089642452</v>
+        <v>34.95890390666784</v>
       </c>
       <c r="D13" t="n">
-        <v>1.500086186683701</v>
+        <v>1.490486148195527</v>
       </c>
       <c r="E13" t="n">
-        <v>9.557833640570065</v>
+        <v>9.686009999209563</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545498675623804</v>
+        <v>0.7546735883235547</v>
       </c>
       <c r="G13" t="n">
-        <v>23.16877527860345</v>
+        <v>23.06270708774167</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70929390786949</v>
+        <v>34.7149850628835</v>
       </c>
       <c r="I13" t="n">
-        <v>2.236579279014447</v>
+        <v>2.302773016532972</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715936672264875</v>
+        <v>4.716709927022216</v>
       </c>
       <c r="K13" t="n">
-        <v>23.3569451674316</v>
+        <v>23.27165517009099</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62132374228298</v>
+        <v>41.69275853581479</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92551980613911</v>
+        <v>99.92331761257363</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.46858602763696</v>
+        <v>83.48846641864797</v>
       </c>
       <c r="C14" t="n">
-        <v>39.28035217053377</v>
+        <v>39.17954669628509</v>
       </c>
       <c r="D14" t="n">
-        <v>1.50173601906444</v>
+        <v>1.492232352849975</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94976542365805</v>
+        <v>12.03717551181806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553797404159788</v>
+        <v>0.7555577391317426</v>
       </c>
       <c r="G14" t="n">
-        <v>25.11667250309024</v>
+        <v>24.94048256354766</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66988368395371</v>
+        <v>36.60641196514505</v>
       </c>
       <c r="I14" t="n">
-        <v>2.754025279854675</v>
+        <v>2.934370416582091</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721123377599865</v>
+        <v>4.722235869573391</v>
       </c>
       <c r="K14" t="n">
-        <v>16.53141397236302</v>
+        <v>16.51153358135202</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09653386838701</v>
+        <v>44.21122183478219</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90830001128381</v>
+        <v>99.90230211241931</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.62784674615112</v>
+        <v>82.75302939591965</v>
       </c>
       <c r="C15" t="n">
-        <v>38.8653179158338</v>
+        <v>38.89756259136663</v>
       </c>
       <c r="D15" t="n">
-        <v>1.470361329294472</v>
+        <v>1.465148177078912</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08296555432822</v>
+        <v>12.22665277079078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560797542056081</v>
+        <v>0.7563026840729079</v>
       </c>
       <c r="G15" t="n">
-        <v>24.59192794223907</v>
+        <v>24.48781015480639</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70386582944882</v>
+        <v>36.64250419211236</v>
       </c>
       <c r="I15" t="n">
-        <v>2.297147872849882</v>
+        <v>2.447719641602631</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725498463785048</v>
+        <v>4.726891775455673</v>
       </c>
       <c r="K15" t="n">
-        <v>17.37215325384886</v>
+        <v>17.24697060408035</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68602812809915</v>
+        <v>43.77395651520352</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9234992977818</v>
+        <v>99.91848971065049</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.07604884336467</v>
+        <v>80.29539091544748</v>
       </c>
       <c r="C16" t="n">
-        <v>36.66858499295449</v>
+        <v>36.81823636761052</v>
       </c>
       <c r="D16" t="n">
-        <v>1.373092935592163</v>
+        <v>1.371997714627654</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60294733612321</v>
+        <v>11.7895618951947</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566827268872023</v>
+        <v>0.756943645807485</v>
       </c>
       <c r="G16" t="n">
-        <v>22.9651051461497</v>
+        <v>22.93093633410752</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73313711767067</v>
+        <v>36.67355848233349</v>
       </c>
       <c r="I16" t="n">
-        <v>1.915816537896715</v>
+        <v>2.041495057079859</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729267043045011</v>
+        <v>4.730897786296779</v>
       </c>
       <c r="K16" t="n">
-        <v>19.92395115663534</v>
+        <v>19.70460908455252</v>
       </c>
       <c r="L16" t="n">
-        <v>43.34365418727543</v>
+        <v>43.40916233557022</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93619033686527</v>
+        <v>99.93200778773326</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.69768006628546</v>
+        <v>82.10614601611438</v>
       </c>
       <c r="C17" t="n">
-        <v>37.86204957249186</v>
+        <v>38.14261836287332</v>
       </c>
       <c r="D17" t="n">
-        <v>1.374150004211656</v>
+        <v>1.373119953497334</v>
       </c>
       <c r="E17" t="n">
-        <v>12.35167501470801</v>
+        <v>12.61422235360191</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757265255239633</v>
+        <v>0.7575627952218208</v>
       </c>
       <c r="G17" t="n">
-        <v>23.40810720481094</v>
+        <v>23.42891238607688</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18673842578693</v>
+        <v>37.18277544569914</v>
       </c>
       <c r="I17" t="n">
-        <v>1.886836316280576</v>
+        <v>2.014785611880919</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732907845247703</v>
+        <v>4.734767470136378</v>
       </c>
       <c r="K17" t="n">
-        <v>18.30231993371455</v>
+        <v>17.89385398388562</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77278433171613</v>
+        <v>43.89642302173079</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93715383792254</v>
+        <v>99.93289536848972</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.28726365038759</v>
+        <v>79.76146742649287</v>
       </c>
       <c r="C18" t="n">
-        <v>35.74284166255575</v>
+        <v>36.10897023375987</v>
       </c>
       <c r="D18" t="n">
-        <v>1.285801938378901</v>
+        <v>1.287977531498954</v>
       </c>
       <c r="E18" t="n">
-        <v>11.81978416148372</v>
+        <v>12.11208584993792</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577661696300126</v>
+        <v>0.7580947279121293</v>
       </c>
       <c r="G18" t="n">
-        <v>21.90313250043924</v>
+        <v>21.97616651325079</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21133663926613</v>
+        <v>37.20888382100574</v>
       </c>
       <c r="I18" t="n">
-        <v>1.573403681001985</v>
+        <v>1.680166933436525</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736038560187576</v>
+        <v>4.738092049450807</v>
       </c>
       <c r="K18" t="n">
-        <v>20.71273634961244</v>
+        <v>20.23853257350715</v>
       </c>
       <c r="L18" t="n">
-        <v>43.49200986793512</v>
+        <v>43.59653092573628</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9475878801033</v>
+        <v>99.94403373300329</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.31704166418861</v>
+        <v>78.82053097431157</v>
       </c>
       <c r="C19" t="n">
-        <v>35.01097834646845</v>
+        <v>35.42674468895137</v>
       </c>
       <c r="D19" t="n">
-        <v>1.250704890732174</v>
+        <v>1.254462717615688</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7164191434054</v>
+        <v>12.03040874333858</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581904765694557</v>
+        <v>0.7585438777878961</v>
       </c>
       <c r="G19" t="n">
-        <v>21.30526803777581</v>
+        <v>21.40431870337315</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23217291963175</v>
+        <v>37.23092904164941</v>
       </c>
       <c r="I19" t="n">
-        <v>1.315595717514926</v>
+        <v>1.40096865437251</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738690478559096</v>
+        <v>4.74089923617435</v>
       </c>
       <c r="K19" t="n">
-        <v>21.6829583358114</v>
+        <v>21.17946902568842</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26223466874382</v>
+        <v>43.34711498165365</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95617135102366</v>
+        <v>99.95332869629344</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.81467475831097</v>
+        <v>76.28612964084438</v>
       </c>
       <c r="C20" t="n">
-        <v>32.71093727003782</v>
+        <v>33.10791168842205</v>
       </c>
       <c r="D20" t="n">
-        <v>1.159944952406906</v>
+        <v>1.163404829365165</v>
       </c>
       <c r="E20" t="n">
-        <v>11.04900315903064</v>
+        <v>11.35183380830441</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585561171493733</v>
+        <v>0.758931030803491</v>
       </c>
       <c r="G20" t="n">
-        <v>19.75920802998305</v>
+        <v>19.85063995851991</v>
       </c>
       <c r="H20" t="n">
-        <v>37.25012829327285</v>
+        <v>37.24993132599176</v>
       </c>
       <c r="I20" t="n">
-        <v>1.096858474284558</v>
+        <v>1.168069745337802</v>
       </c>
       <c r="J20" t="n">
-        <v>4.740975732183581</v>
+        <v>4.743318942521818</v>
       </c>
       <c r="K20" t="n">
-        <v>24.18532524168904</v>
+        <v>23.71387035915564</v>
       </c>
       <c r="L20" t="n">
-        <v>43.06719316278662</v>
+        <v>43.13930215646752</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96345567451348</v>
+        <v>99.96108420404519</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.74696380103865</v>
+        <v>82.17384733779923</v>
       </c>
       <c r="C21" t="n">
-        <v>36.4670304128731</v>
+        <v>36.78863452782009</v>
       </c>
       <c r="D21" t="n">
-        <v>1.160651704160105</v>
+        <v>1.164180326715368</v>
       </c>
       <c r="E21" t="n">
-        <v>13.05155443738471</v>
+        <v>13.3294719409364</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590183036217419</v>
+        <v>0.7594369157616063</v>
       </c>
       <c r="G21" t="n">
-        <v>21.51802524425477</v>
+        <v>21.56006775300756</v>
       </c>
       <c r="H21" t="n">
-        <v>39.01960268445239</v>
+        <v>38.97095706472916</v>
       </c>
       <c r="I21" t="n">
-        <v>1.494247029529056</v>
+        <v>1.643252613139096</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743864397635885</v>
+        <v>4.746480723510039</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25303619896136</v>
+        <v>17.82615266220076</v>
       </c>
       <c r="L21" t="n">
-        <v>45.23015548340914</v>
+        <v>45.33047421029313</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95022209524359</v>
+        <v>99.94526140031398</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.41862731346671</v>
+        <v>45.30588559481191</v>
       </c>
       <c r="M2" t="n">
-        <v>99.90566039343142</v>
+        <v>100.541007312933</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02520265101752</v>
+        <v>88.10346757800009</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93520242356725</v>
+        <v>45.94351100892982</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228720267933066</v>
+        <v>2.228914590888073</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709922926368889</v>
+        <v>5.719057960539645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429067559776886</v>
+        <v>0.7429715302960243</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97541532180885</v>
+        <v>33.97745677012229</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17371077497367</v>
+        <v>34.17669039361711</v>
       </c>
       <c r="I3" t="n">
-        <v>6.551359379094811</v>
+        <v>6.614804268186791</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643167224860553</v>
+        <v>4.643572064350152</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97479734898246</v>
+        <v>11.89653242199991</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8548389297906</v>
+        <v>48.92253861522929</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648387023403</v>
+        <v>106.762582046159</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13943999577191</v>
+        <v>87.25264816296531</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68111364171715</v>
+        <v>42.7363042518372</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186186739716586</v>
+        <v>2.188290109160445</v>
       </c>
       <c r="E4" t="n">
-        <v>6.51276840354611</v>
+        <v>6.535483308464221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444614910513473</v>
+        <v>0.7445394491914633</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32701888235935</v>
+        <v>33.35817930774133</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24522858836197</v>
+        <v>34.24881466280731</v>
       </c>
       <c r="I4" t="n">
-        <v>5.470891571665632</v>
+        <v>5.523969768153902</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652884319070919</v>
+        <v>4.653371557446646</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86056000422809</v>
+        <v>12.74735183703469</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2763441490799</v>
+        <v>44.33259934812293</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81801779502514</v>
+        <v>99.81625543699481</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.97274562959811</v>
+        <v>86.19847292429574</v>
       </c>
       <c r="C5" t="n">
-        <v>42.36358720211982</v>
+        <v>42.53953495924264</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129259194042513</v>
+        <v>2.137276889937906</v>
       </c>
       <c r="E5" t="n">
-        <v>7.104369736893408</v>
+        <v>7.151714917132906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745779764197223</v>
+        <v>0.7458671820983724</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45919485107272</v>
+        <v>32.58053647749362</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30586915307225</v>
+        <v>34.30989037652513</v>
       </c>
       <c r="I5" t="n">
-        <v>4.567149404087351</v>
+        <v>4.611517192992984</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661123526232643</v>
+        <v>4.661669888114829</v>
       </c>
       <c r="K5" t="n">
-        <v>14.02725437040189</v>
+        <v>13.80152707570422</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45718921715425</v>
+        <v>43.50549436038222</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84803078967596</v>
+        <v>99.84655639532909</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.60204561357082</v>
+        <v>84.91579552535583</v>
       </c>
       <c r="C6" t="n">
-        <v>41.7022298363018</v>
+        <v>41.97320656674969</v>
       </c>
       <c r="D6" t="n">
-        <v>2.062349927759335</v>
+        <v>2.074931275945619</v>
       </c>
       <c r="E6" t="n">
-        <v>7.516402880200666</v>
+        <v>7.58455137235493</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468997800907236</v>
+        <v>0.746994042159884</v>
       </c>
       <c r="G6" t="n">
-        <v>31.43920587194583</v>
+        <v>31.63014321752325</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35738988417327</v>
+        <v>34.36172593935466</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81167364383397</v>
+        <v>3.848736914518224</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668123625567021</v>
+        <v>4.668712763499276</v>
       </c>
       <c r="K6" t="n">
-        <v>15.3979543864292</v>
+        <v>15.08420447464414</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77295051604435</v>
+        <v>42.81449125880079</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87313473877533</v>
+        <v>99.87190230019462</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.02760918428663</v>
+        <v>83.455825297361</v>
       </c>
       <c r="C7" t="n">
-        <v>40.71982114791155</v>
+        <v>41.11119647367194</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985720795395159</v>
+        <v>2.004130611054885</v>
       </c>
       <c r="E7" t="n">
-        <v>7.767196832139536</v>
+        <v>7.860984264696519</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478534700035221</v>
+        <v>0.7479521908427799</v>
       </c>
       <c r="G7" t="n">
-        <v>30.27104374981586</v>
+        <v>30.55086160643991</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40125962016201</v>
+        <v>34.40580077876787</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180450529248553</v>
+        <v>3.211394652791673</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674084187522012</v>
+        <v>4.674701192767374</v>
       </c>
       <c r="K7" t="n">
-        <v>16.97239081571336</v>
+        <v>16.54417470263897</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20190821293527</v>
+        <v>42.23771946495246</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89412017656016</v>
+        <v>99.89309064126337</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.0247627088464</v>
+        <v>88.22899085325766</v>
       </c>
       <c r="C8" t="n">
-        <v>43.08189100247805</v>
+        <v>43.3747594839845</v>
       </c>
       <c r="D8" t="n">
-        <v>1.989999788993635</v>
+        <v>2.008370233628541</v>
       </c>
       <c r="E8" t="n">
-        <v>9.643441885605386</v>
+        <v>9.665691078735463</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494650058338184</v>
+        <v>0.7495344405099528</v>
       </c>
       <c r="G8" t="n">
-        <v>30.79182070480223</v>
+        <v>31.04292053000422</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47539026835563</v>
+        <v>34.47858426345783</v>
       </c>
       <c r="I8" t="n">
-        <v>5.69048876879432</v>
+        <v>5.599300053734439</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684156286461363</v>
+        <v>4.684590253187205</v>
       </c>
       <c r="K8" t="n">
-        <v>11.97523729115361</v>
+        <v>11.77100914674235</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75359661286239</v>
+        <v>44.66798203386222</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81072490649406</v>
+        <v>99.81375066458908</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.10264786495712</v>
+        <v>86.23720439126276</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04295820367835</v>
+        <v>42.25241038390195</v>
       </c>
       <c r="D9" t="n">
-        <v>1.90333523519946</v>
+        <v>1.918184540686378</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01526895108955</v>
+        <v>10.01073976072744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508434206801451</v>
+        <v>0.7508887320271915</v>
       </c>
       <c r="G9" t="n">
-        <v>29.45083593854683</v>
+        <v>29.64894084833526</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53879735128666</v>
+        <v>34.54088167325081</v>
       </c>
       <c r="I9" t="n">
-        <v>4.750795588903573</v>
+        <v>4.674514261065731</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692771379250905</v>
+        <v>4.693054575169947</v>
       </c>
       <c r="K9" t="n">
-        <v>13.89735213504288</v>
+        <v>13.76279560873725</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90162052881226</v>
+        <v>43.82925789475706</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84193086753349</v>
+        <v>99.84446388739626</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.88796224709733</v>
+        <v>84.14564230602296</v>
       </c>
       <c r="C10" t="n">
-        <v>40.56543064833728</v>
+        <v>40.88642988835116</v>
       </c>
       <c r="D10" t="n">
-        <v>1.804279806116059</v>
+        <v>1.824506289791871</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15491585950558</v>
+        <v>10.17208742715475</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752026454928415</v>
+        <v>0.7520492413560834</v>
       </c>
       <c r="G10" t="n">
-        <v>27.91812370960946</v>
+        <v>28.20097749515711</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59321692670707</v>
+        <v>34.59426510237984</v>
       </c>
       <c r="I10" t="n">
-        <v>3.965234146928157</v>
+        <v>3.901448991707793</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700165343302592</v>
+        <v>4.700307758475522</v>
       </c>
       <c r="K10" t="n">
-        <v>16.11203775290263</v>
+        <v>15.85435769397706</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19056505462388</v>
+        <v>43.12936479930887</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86803345586381</v>
+        <v>99.87015238163707</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.51611687795878</v>
+        <v>81.95501274492159</v>
       </c>
       <c r="C11" t="n">
-        <v>38.80822742587208</v>
+        <v>39.30085880787341</v>
       </c>
       <c r="D11" t="n">
-        <v>1.699259905821299</v>
+        <v>1.727361147636688</v>
       </c>
       <c r="E11" t="n">
-        <v>10.11531100333093</v>
+        <v>10.17306391405186</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530439754848447</v>
+        <v>0.7530450338747536</v>
       </c>
       <c r="G11" t="n">
-        <v>26.29312155724853</v>
+        <v>26.6994271946675</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64002287230284</v>
+        <v>34.64007155823867</v>
       </c>
       <c r="I11" t="n">
-        <v>3.308832716990069</v>
+        <v>3.255512434734906</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706524846780278</v>
+        <v>4.706531461717211</v>
       </c>
       <c r="K11" t="n">
-        <v>18.48388312204121</v>
+        <v>18.04498725507843</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59774405911647</v>
+        <v>42.54578035394519</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88985460702976</v>
+        <v>99.89162641689703</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.15803378637759</v>
+        <v>79.72655320039139</v>
       </c>
       <c r="C12" t="n">
-        <v>36.96221344988633</v>
+        <v>37.57659225052491</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5959637419158</v>
+        <v>1.629484822524682</v>
       </c>
       <c r="E12" t="n">
-        <v>9.960506559445522</v>
+        <v>10.04930225444527</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539193667564328</v>
+        <v>0.7539001551302105</v>
       </c>
       <c r="G12" t="n">
-        <v>24.69479125788679</v>
+        <v>25.18657516601967</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68029087079589</v>
+        <v>34.67940713598968</v>
       </c>
       <c r="I12" t="n">
-        <v>2.760565947349428</v>
+        <v>2.716007696718064</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711996042227704</v>
+        <v>4.711875969563816</v>
       </c>
       <c r="K12" t="n">
-        <v>20.84196621362242</v>
+        <v>20.27344679960861</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10390831657484</v>
+        <v>42.05953004890164</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90808798008361</v>
+        <v>99.90956909903515</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.72834482990901</v>
+        <v>77.53163894104053</v>
       </c>
       <c r="C13" t="n">
-        <v>34.95890390666784</v>
+        <v>35.80157142997981</v>
       </c>
       <c r="D13" t="n">
-        <v>1.490486148195527</v>
+        <v>1.533960149425388</v>
       </c>
       <c r="E13" t="n">
-        <v>9.686009999209563</v>
+        <v>9.83777652322757</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546735883235547</v>
+        <v>0.7546344765112076</v>
       </c>
       <c r="G13" t="n">
-        <v>23.06270708774167</v>
+        <v>23.71007208604798</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7149850628835</v>
+        <v>34.71318591951555</v>
       </c>
       <c r="I13" t="n">
-        <v>2.302773016532972</v>
+        <v>2.265544308117796</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716709927022216</v>
+        <v>4.716465478195048</v>
       </c>
       <c r="K13" t="n">
-        <v>23.27165517009099</v>
+        <v>22.46836105895947</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69275853581479</v>
+        <v>41.65462285281854</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92331761257363</v>
+        <v>99.92455534175782</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.48846641864797</v>
+        <v>84.02623835860327</v>
       </c>
       <c r="C14" t="n">
-        <v>39.17954669628509</v>
+        <v>39.88564988950952</v>
       </c>
       <c r="D14" t="n">
-        <v>1.492232352849975</v>
+        <v>1.535682817919289</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03717551181806</v>
+        <v>12.11160948771555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555577391317426</v>
+        <v>0.755481946399903</v>
       </c>
       <c r="G14" t="n">
-        <v>24.94048256354766</v>
+        <v>25.52766803475389</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60641196514505</v>
+        <v>36.54313858918504</v>
       </c>
       <c r="I14" t="n">
-        <v>2.934370416582091</v>
+        <v>2.83089531763019</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722235869573391</v>
+        <v>4.721762164999395</v>
       </c>
       <c r="K14" t="n">
-        <v>16.51153358135202</v>
+        <v>15.97376164139675</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21122183478219</v>
+        <v>44.04633114473464</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90230211241931</v>
+        <v>99.90574267564091</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.75302939591965</v>
+        <v>83.42129524072341</v>
       </c>
       <c r="C15" t="n">
-        <v>38.89756259136663</v>
+        <v>39.7186790741352</v>
       </c>
       <c r="D15" t="n">
-        <v>1.465148177078912</v>
+        <v>1.513395253361951</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22665277079078</v>
+        <v>12.32938300403588</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563026840729079</v>
+        <v>0.7561947633959631</v>
       </c>
       <c r="G15" t="n">
-        <v>24.48781015480639</v>
+        <v>25.15718166694147</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64250419211236</v>
+        <v>36.57761799719722</v>
       </c>
       <c r="I15" t="n">
-        <v>2.447719641602631</v>
+        <v>2.361305284566158</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726891775455673</v>
+        <v>4.726217271224771</v>
       </c>
       <c r="K15" t="n">
-        <v>17.24697060408035</v>
+        <v>16.57870475927659</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77395651520352</v>
+        <v>43.62398018554293</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91848971065049</v>
+        <v>99.92136401895472</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.29539091544748</v>
+        <v>81.22723638388743</v>
       </c>
       <c r="C16" t="n">
-        <v>36.81823636761052</v>
+        <v>37.89005489820013</v>
       </c>
       <c r="D16" t="n">
-        <v>1.371997714627654</v>
+        <v>1.429408959846559</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7895618951947</v>
+        <v>11.97338455212287</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756943645807485</v>
+        <v>0.7568058917943927</v>
       </c>
       <c r="G16" t="n">
-        <v>22.93093633410752</v>
+        <v>23.76107682334152</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67355848233349</v>
+        <v>36.60717866355863</v>
       </c>
       <c r="I16" t="n">
-        <v>2.041495057079859</v>
+        <v>1.969344669508506</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730897786296779</v>
+        <v>4.730036823714955</v>
       </c>
       <c r="K16" t="n">
-        <v>19.70460908455252</v>
+        <v>18.77276361611257</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40916233557022</v>
+        <v>43.27158967222712</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93200778773326</v>
+        <v>99.93440818653983</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.10614601611438</v>
+        <v>82.8099118579037</v>
       </c>
       <c r="C17" t="n">
-        <v>38.14261836287332</v>
+        <v>39.05804539712105</v>
       </c>
       <c r="D17" t="n">
-        <v>1.373119953497334</v>
+        <v>1.430527864108779</v>
       </c>
       <c r="E17" t="n">
-        <v>12.61422235360191</v>
+        <v>12.71394037191767</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575627952218208</v>
+        <v>0.7573982998188205</v>
       </c>
       <c r="G17" t="n">
-        <v>23.42891238607688</v>
+        <v>24.18675248624698</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18277544569914</v>
+        <v>37.04290992182252</v>
       </c>
       <c r="I17" t="n">
-        <v>2.014785611880919</v>
+        <v>1.94464354012129</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734767470136378</v>
+        <v>4.733739373867628</v>
       </c>
       <c r="K17" t="n">
-        <v>17.89385398388562</v>
+        <v>17.19008814209629</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89642302173079</v>
+        <v>43.68709571030894</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93289536848972</v>
+        <v>99.93522924952629</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.76146742649287</v>
+        <v>80.62830156195757</v>
       </c>
       <c r="C18" t="n">
-        <v>36.10897023375987</v>
+        <v>37.17709810671852</v>
       </c>
       <c r="D18" t="n">
-        <v>1.287977531498954</v>
+        <v>1.350014244024787</v>
       </c>
       <c r="E18" t="n">
-        <v>12.11208584993792</v>
+        <v>12.26863904697272</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580947279121293</v>
+        <v>0.7579060678765354</v>
       </c>
       <c r="G18" t="n">
-        <v>21.97616651325079</v>
+        <v>22.82546267875592</v>
       </c>
       <c r="H18" t="n">
-        <v>37.20888382100574</v>
+        <v>37.06774389151537</v>
       </c>
       <c r="I18" t="n">
-        <v>1.680166933436525</v>
+        <v>1.621622708583888</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738092049450807</v>
+        <v>4.736912924228347</v>
       </c>
       <c r="K18" t="n">
-        <v>20.23853257350715</v>
+        <v>19.37169843804243</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59653092573628</v>
+        <v>43.39718557912456</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94403373300329</v>
+        <v>99.94598212388551</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.82053097431157</v>
+        <v>79.78010099791945</v>
       </c>
       <c r="C19" t="n">
-        <v>35.42674468895137</v>
+        <v>36.57904684978405</v>
       </c>
       <c r="D19" t="n">
-        <v>1.254462717615688</v>
+        <v>1.319338923869555</v>
       </c>
       <c r="E19" t="n">
-        <v>12.03040874333858</v>
+        <v>12.21522094974935</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585438777878961</v>
+        <v>0.7583342350792308</v>
       </c>
       <c r="G19" t="n">
-        <v>21.40431870337315</v>
+        <v>22.30681750263192</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23092904164941</v>
+        <v>37.0886847348269</v>
       </c>
       <c r="I19" t="n">
-        <v>1.40096865437251</v>
+        <v>1.352115682517312</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74089923617435</v>
+        <v>4.739588969245193</v>
       </c>
       <c r="K19" t="n">
-        <v>21.17946902568842</v>
+        <v>20.21989900208055</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34711498165365</v>
+        <v>43.15600907289696</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95332869629344</v>
+        <v>99.95495492476155</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.28612964084438</v>
+        <v>77.3914008412395</v>
       </c>
       <c r="C20" t="n">
-        <v>33.10791168842205</v>
+        <v>34.39880529944417</v>
       </c>
       <c r="D20" t="n">
-        <v>1.163404829365165</v>
+        <v>1.232007588064246</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35183380830441</v>
+        <v>11.59454076033721</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758931030803491</v>
+        <v>0.7587024404529508</v>
       </c>
       <c r="G20" t="n">
-        <v>19.85063995851991</v>
+        <v>20.83025667749045</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24993132599176</v>
+        <v>37.10669295915841</v>
       </c>
       <c r="I20" t="n">
-        <v>1.168069745337802</v>
+        <v>1.127310162905291</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743318942521818</v>
+        <v>4.741890252830943</v>
       </c>
       <c r="K20" t="n">
-        <v>23.71387035915564</v>
+        <v>22.6085991587605</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13930215646752</v>
+        <v>42.95503677283651</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96108420404519</v>
+        <v>99.96244123104118</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17384733779923</v>
+        <v>82.68961831170235</v>
       </c>
       <c r="C21" t="n">
-        <v>36.78863452782009</v>
+        <v>37.69652638848522</v>
       </c>
       <c r="D21" t="n">
-        <v>1.164180326715368</v>
+        <v>1.232794348309731</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3294719409364</v>
+        <v>13.37551613577571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594369157616063</v>
+        <v>0.7591869479544335</v>
       </c>
       <c r="G21" t="n">
-        <v>21.56006775300756</v>
+        <v>22.35310196430883</v>
       </c>
       <c r="H21" t="n">
-        <v>38.97095706472916</v>
+        <v>38.63993238082519</v>
       </c>
       <c r="I21" t="n">
-        <v>1.643252613139096</v>
+        <v>1.584168109813249</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746480723510039</v>
+        <v>4.74491842471521</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82615266220076</v>
+        <v>17.31038168829765</v>
       </c>
       <c r="L21" t="n">
-        <v>45.33047421029313</v>
+        <v>44.94032001970282</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94526140031398</v>
+        <v>99.9472280964857</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_66_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30588559481191</v>
+        <v>43.83024821818208</v>
       </c>
       <c r="M2" t="n">
-        <v>100.541007312933</v>
+        <v>93.88832777006735</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10346757800009</v>
+        <v>81.49265737943308</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94351100892982</v>
+        <v>43.24821293498864</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228914590888073</v>
+        <v>2.181308571577823</v>
       </c>
       <c r="E3" t="n">
-        <v>5.719057960539645</v>
+        <v>4.147767131219681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429715302960243</v>
+        <v>0.7376440971695648</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97745677012229</v>
+        <v>32.81051643081642</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17669039361711</v>
+        <v>33.93162846979997</v>
       </c>
       <c r="I3" t="n">
-        <v>6.614804268186791</v>
+        <v>3.073517071539853</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643572064350152</v>
+        <v>4.610275607309779</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89653242199991</v>
+        <v>18.50734262056691</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92253861522929</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.762582046159</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.25264816296531</v>
+        <v>88.65193475204957</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7363042518372</v>
+        <v>42.85199432263227</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188290109160445</v>
+        <v>2.187084673183807</v>
       </c>
       <c r="E4" t="n">
-        <v>6.535483308464221</v>
+        <v>6.538424211821864</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445394491914633</v>
+        <v>0.7395973775581455</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35817930774133</v>
+        <v>33.50036007244291</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24881466280731</v>
+        <v>34.02147936767469</v>
       </c>
       <c r="I4" t="n">
-        <v>5.523969768153902</v>
+        <v>7.042505439629745</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653371557446646</v>
+        <v>4.622483609738408</v>
       </c>
       <c r="K4" t="n">
-        <v>12.74735183703469</v>
+        <v>11.34806524795043</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33259934812293</v>
+        <v>45.56581022450415</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81625543699481</v>
+        <v>99.76586979508686</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.19847292429574</v>
+        <v>87.69650877417534</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53953495924264</v>
+        <v>42.98816611263663</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137276889937906</v>
+        <v>2.142377494794433</v>
       </c>
       <c r="E5" t="n">
-        <v>7.151714917132906</v>
+        <v>7.38508189582397</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458671820983724</v>
+        <v>0.7412508905599323</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58053647749362</v>
+        <v>32.81556419223277</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30989037652513</v>
+        <v>34.09754096575688</v>
       </c>
       <c r="I5" t="n">
-        <v>4.611517192992984</v>
+        <v>5.881875269007778</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661669888114829</v>
+        <v>4.632818065999576</v>
       </c>
       <c r="K5" t="n">
-        <v>13.80152707570422</v>
+        <v>12.30349122582466</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50549436038222</v>
+        <v>44.51271751043788</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84655639532909</v>
+        <v>99.80437484889917</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.91579552535583</v>
+        <v>86.46874460651611</v>
       </c>
       <c r="C6" t="n">
-        <v>41.97320656674969</v>
+        <v>42.67343742644741</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074931275945619</v>
+        <v>2.084195986737796</v>
       </c>
       <c r="E6" t="n">
-        <v>7.58455137235493</v>
+        <v>8.002995561657652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746994042159884</v>
+        <v>0.742654159050962</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63014321752325</v>
+        <v>31.92437717357121</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36172593935466</v>
+        <v>34.16209131634425</v>
       </c>
       <c r="I6" t="n">
-        <v>3.848736914518224</v>
+        <v>4.910841915085745</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668712763499276</v>
+        <v>4.641588494068512</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08420447464414</v>
+        <v>13.53125539348388</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81449125880079</v>
+        <v>43.6319217559296</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87190230019462</v>
+        <v>99.83661457586089</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.455825297361</v>
+        <v>85.14352126607137</v>
       </c>
       <c r="C7" t="n">
-        <v>41.11119647367194</v>
+        <v>42.11106091766814</v>
       </c>
       <c r="D7" t="n">
-        <v>2.004130611054885</v>
+        <v>2.021690633502979</v>
       </c>
       <c r="E7" t="n">
-        <v>7.860984264696519</v>
+        <v>8.44614040489644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479521908427799</v>
+        <v>0.7438459081280503</v>
       </c>
       <c r="G7" t="n">
-        <v>30.55086160643991</v>
+        <v>30.96696026809155</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40580077876787</v>
+        <v>34.2169117738903</v>
       </c>
       <c r="I7" t="n">
-        <v>3.211394652791673</v>
+        <v>4.098935351761742</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674701192767374</v>
+        <v>4.649036925800313</v>
       </c>
       <c r="K7" t="n">
-        <v>16.54417470263897</v>
+        <v>14.85647873392861</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23771946495246</v>
+        <v>42.89604807298421</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89309064126337</v>
+        <v>99.86358772458097</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.22899085325766</v>
+        <v>83.55606522696402</v>
       </c>
       <c r="C8" t="n">
-        <v>43.3747594839845</v>
+        <v>41.16047775214523</v>
       </c>
       <c r="D8" t="n">
-        <v>2.008370233628541</v>
+        <v>1.94688827944848</v>
       </c>
       <c r="E8" t="n">
-        <v>9.665691078735463</v>
+        <v>8.703707441258391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495344405099528</v>
+        <v>0.7448609074905759</v>
       </c>
       <c r="G8" t="n">
-        <v>31.04292053000422</v>
+        <v>29.82118579222541</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47858426345783</v>
+        <v>34.26360174456648</v>
       </c>
       <c r="I8" t="n">
-        <v>5.599300053734439</v>
+        <v>3.420440390158589</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684590253187205</v>
+        <v>4.655380671816098</v>
       </c>
       <c r="K8" t="n">
-        <v>11.77100914674235</v>
+        <v>16.44393477303597</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66798203386222</v>
+        <v>42.28172815949206</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81375066458908</v>
+        <v>99.88614068467328</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.23720439126276</v>
+        <v>81.82983317993811</v>
       </c>
       <c r="C9" t="n">
-        <v>42.25241038390195</v>
+        <v>39.96547153869673</v>
       </c>
       <c r="D9" t="n">
-        <v>1.918184540686378</v>
+        <v>1.866014796567664</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01073976072744</v>
+        <v>8.817769977492734</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508887320271915</v>
+        <v>0.7457267673202042</v>
       </c>
       <c r="G9" t="n">
-        <v>29.64894084833526</v>
+        <v>28.58241765945079</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54088167325081</v>
+        <v>34.30343129672938</v>
       </c>
       <c r="I9" t="n">
-        <v>4.674514261065731</v>
+        <v>2.85368038662607</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693054575169947</v>
+        <v>4.660792295751275</v>
       </c>
       <c r="K9" t="n">
-        <v>13.76279560873725</v>
+        <v>18.1701668200619</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82925789475706</v>
+        <v>41.7693494081814</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84446388739626</v>
+        <v>99.90498776694002</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.14564230602296</v>
+        <v>86.30539510644337</v>
       </c>
       <c r="C10" t="n">
-        <v>40.88642988835116</v>
+        <v>43.03151310955305</v>
       </c>
       <c r="D10" t="n">
-        <v>1.824506289791871</v>
+        <v>1.868141290907465</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17208742715475</v>
+        <v>10.58521333866277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520492413560834</v>
+        <v>0.7465765911011633</v>
       </c>
       <c r="G10" t="n">
-        <v>28.20097749515711</v>
+        <v>29.88062022942904</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59426510237984</v>
+        <v>35.60815348441912</v>
       </c>
       <c r="I10" t="n">
-        <v>3.901448991707793</v>
+        <v>2.950586477541529</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700307758475522</v>
+        <v>4.666103694382269</v>
       </c>
       <c r="K10" t="n">
-        <v>15.85435769397706</v>
+        <v>13.69460489355665</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12936479930887</v>
+        <v>43.17564106881842</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87015238163707</v>
+        <v>99.90175907192811</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.95501274492159</v>
+        <v>86.12263295382078</v>
       </c>
       <c r="C11" t="n">
-        <v>39.30085880787341</v>
+        <v>43.22365736410881</v>
       </c>
       <c r="D11" t="n">
-        <v>1.727361147636688</v>
+        <v>1.854505202780872</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17306391405186</v>
+        <v>10.96343011918237</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530450338747536</v>
+        <v>0.7473006937388847</v>
       </c>
       <c r="G11" t="n">
-        <v>26.6994271946675</v>
+        <v>29.70034385800902</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64007155823867</v>
+        <v>35.68052040762346</v>
       </c>
       <c r="I11" t="n">
-        <v>3.255512434734906</v>
+        <v>2.505903336618132</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706531461717211</v>
+        <v>4.670629335868028</v>
       </c>
       <c r="K11" t="n">
-        <v>18.04498725507843</v>
+        <v>13.87736704617924</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54578035394519</v>
+        <v>42.81552641562197</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89162641689703</v>
+        <v>99.91655082591002</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.72655320039139</v>
+        <v>84.3919197434811</v>
       </c>
       <c r="C12" t="n">
-        <v>37.57659225052491</v>
+        <v>41.88290879345734</v>
       </c>
       <c r="D12" t="n">
-        <v>1.629484822524682</v>
+        <v>1.780485864491972</v>
       </c>
       <c r="E12" t="n">
-        <v>10.04930225444527</v>
+        <v>10.87417338204608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539001551302105</v>
+        <v>0.7479175936345345</v>
       </c>
       <c r="G12" t="n">
-        <v>25.18657516601967</v>
+        <v>28.51490647232464</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67940713598968</v>
+        <v>35.70997482871608</v>
       </c>
       <c r="I12" t="n">
-        <v>2.716007696718064</v>
+        <v>2.08997664205195</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711875969563816</v>
+        <v>4.67448496021584</v>
       </c>
       <c r="K12" t="n">
-        <v>20.27344679960861</v>
+        <v>15.6080802565189</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05953004890164</v>
+        <v>42.4394025240066</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90956909903515</v>
+        <v>99.93039157398285</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.53163894104053</v>
+        <v>85.56474500340546</v>
       </c>
       <c r="C13" t="n">
-        <v>35.80157142997981</v>
+        <v>42.86323479082532</v>
       </c>
       <c r="D13" t="n">
-        <v>1.533960149425388</v>
+        <v>1.781833366505653</v>
       </c>
       <c r="E13" t="n">
-        <v>9.83777652322757</v>
+        <v>11.51752890039523</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546344765112076</v>
+        <v>0.7484836304021322</v>
       </c>
       <c r="G13" t="n">
-        <v>23.71007208604798</v>
+        <v>28.84782851932637</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71318591951555</v>
+        <v>36.04834222594057</v>
       </c>
       <c r="I13" t="n">
-        <v>2.265544308117796</v>
+        <v>1.942705670822183</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716465478195048</v>
+        <v>4.678022690013326</v>
       </c>
       <c r="K13" t="n">
-        <v>22.46836105895947</v>
+        <v>14.43525499659453</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65462285281854</v>
+        <v>42.63680232891404</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92455534175782</v>
+        <v>99.93529211633388</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.02623835860327</v>
+        <v>83.79128649802291</v>
       </c>
       <c r="C14" t="n">
-        <v>39.88564988950952</v>
+        <v>41.39203614330545</v>
       </c>
       <c r="D14" t="n">
-        <v>1.535682817919289</v>
+        <v>1.707957821603201</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11160948771555</v>
+        <v>11.31000152695449</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755481946399903</v>
+        <v>0.7489659864673477</v>
       </c>
       <c r="G14" t="n">
-        <v>25.52766803475389</v>
+        <v>27.651785673133</v>
       </c>
       <c r="H14" t="n">
-        <v>36.54313858918504</v>
+        <v>36.07157337730764</v>
       </c>
       <c r="I14" t="n">
-        <v>2.83089531763019</v>
+        <v>1.619964697136306</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721762164999395</v>
+        <v>4.681037415420923</v>
       </c>
       <c r="K14" t="n">
-        <v>15.97376164139675</v>
+        <v>16.20871350197709</v>
       </c>
       <c r="L14" t="n">
-        <v>44.04633114473464</v>
+        <v>42.34528630830572</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90574267564091</v>
+        <v>99.94603595358828</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.42129524072341</v>
+        <v>83.0377558651053</v>
       </c>
       <c r="C15" t="n">
-        <v>39.7186790741352</v>
+        <v>40.87538953351588</v>
       </c>
       <c r="D15" t="n">
-        <v>1.513395253361951</v>
+        <v>1.676509759976989</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32938300403588</v>
+        <v>11.32925873461106</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561947633959631</v>
+        <v>0.749376385676872</v>
       </c>
       <c r="G15" t="n">
-        <v>25.15718166694147</v>
+        <v>27.14264250289521</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57761799719722</v>
+        <v>36.09133895474083</v>
       </c>
       <c r="I15" t="n">
-        <v>2.361305284566158</v>
+        <v>1.365027116723878</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726217271224771</v>
+        <v>4.683602410480451</v>
       </c>
       <c r="K15" t="n">
-        <v>16.57870475927659</v>
+        <v>16.96224413489469</v>
       </c>
       <c r="L15" t="n">
-        <v>43.62398018554293</v>
+        <v>42.11689034646488</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92136401895472</v>
+        <v>99.95452401487546</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.22723638388743</v>
+        <v>80.87520129209861</v>
       </c>
       <c r="C16" t="n">
-        <v>37.89005489820013</v>
+        <v>38.92481990969841</v>
       </c>
       <c r="D16" t="n">
-        <v>1.429408959846559</v>
+        <v>1.586950238356153</v>
       </c>
       <c r="E16" t="n">
-        <v>11.97338455212287</v>
+        <v>10.91372325803484</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568058917943927</v>
+        <v>0.7497278870846944</v>
       </c>
       <c r="G16" t="n">
-        <v>23.76107682334152</v>
+        <v>25.69267654616971</v>
       </c>
       <c r="H16" t="n">
-        <v>36.60717866355863</v>
+        <v>36.10826790619335</v>
       </c>
       <c r="I16" t="n">
-        <v>1.969344669508506</v>
+        <v>1.138056161980519</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730036823714955</v>
+        <v>4.685799294279341</v>
       </c>
       <c r="K16" t="n">
-        <v>18.77276361611257</v>
+        <v>19.12479870790139</v>
       </c>
       <c r="L16" t="n">
-        <v>43.27158967222712</v>
+        <v>41.91246396249119</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93440818653983</v>
+        <v>99.96208258009099</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.8099118579037</v>
+        <v>85.24427310030819</v>
       </c>
       <c r="C17" t="n">
-        <v>39.05804539712105</v>
+        <v>41.77873733930004</v>
       </c>
       <c r="D17" t="n">
-        <v>1.430527864108779</v>
+        <v>1.587769551348486</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71394037191767</v>
+        <v>12.4479446103608</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573982998188205</v>
+        <v>0.75011495769583</v>
       </c>
       <c r="G17" t="n">
-        <v>24.18675248624698</v>
+        <v>27.01447780757197</v>
       </c>
       <c r="H17" t="n">
-        <v>37.04290992182252</v>
+        <v>37.43544654435124</v>
       </c>
       <c r="I17" t="n">
-        <v>1.94464354012129</v>
+        <v>1.320301143380919</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733739373867628</v>
+        <v>4.688218485598938</v>
       </c>
       <c r="K17" t="n">
-        <v>17.19008814209629</v>
+        <v>14.75572689969182</v>
       </c>
       <c r="L17" t="n">
-        <v>43.68709571030894</v>
+        <v>43.42154843273769</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93522924952629</v>
+        <v>99.95601267172955</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.62830156195757</v>
+        <v>86.89797802072673</v>
       </c>
       <c r="C18" t="n">
-        <v>37.17709810671852</v>
+        <v>42.53347382195068</v>
       </c>
       <c r="D18" t="n">
-        <v>1.350014244024787</v>
+        <v>1.589091419700173</v>
       </c>
       <c r="E18" t="n">
-        <v>12.26863904697272</v>
+        <v>13.06806829443933</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579060678765354</v>
+        <v>0.7507394521143453</v>
       </c>
       <c r="G18" t="n">
-        <v>22.82546267875592</v>
+        <v>27.16098511742587</v>
       </c>
       <c r="H18" t="n">
-        <v>37.06774389151537</v>
+        <v>37.46661273718838</v>
       </c>
       <c r="I18" t="n">
-        <v>1.621622708583888</v>
+        <v>2.17035942414395</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736912924228347</v>
+        <v>4.692121575714658</v>
       </c>
       <c r="K18" t="n">
-        <v>19.37169843804243</v>
+        <v>13.10202197927327</v>
       </c>
       <c r="L18" t="n">
-        <v>43.39718557912456</v>
+        <v>44.2922190642978</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94598212388551</v>
+        <v>99.92771486552175</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.78010099791945</v>
+        <v>84.55224896106164</v>
       </c>
       <c r="C19" t="n">
-        <v>36.57904684978405</v>
+        <v>40.52459403292353</v>
       </c>
       <c r="D19" t="n">
-        <v>1.319338923869555</v>
+        <v>1.501023873625964</v>
       </c>
       <c r="E19" t="n">
-        <v>12.21522094974935</v>
+        <v>12.64548902583684</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583342350792308</v>
+        <v>0.7512751291255879</v>
       </c>
       <c r="G19" t="n">
-        <v>22.30681750263192</v>
+        <v>25.65572161993551</v>
       </c>
       <c r="H19" t="n">
-        <v>37.0886847348269</v>
+        <v>37.49334638369639</v>
       </c>
       <c r="I19" t="n">
-        <v>1.352115682517312</v>
+        <v>1.809923371806422</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739588969245193</v>
+        <v>4.695469557034925</v>
       </c>
       <c r="K19" t="n">
-        <v>20.21989900208055</v>
+        <v>15.44775103893835</v>
       </c>
       <c r="L19" t="n">
-        <v>43.15600907289696</v>
+        <v>43.96736716635633</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95495492476155</v>
+        <v>99.93971223821822</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.3914008412395</v>
+        <v>82.08582383863649</v>
       </c>
       <c r="C20" t="n">
-        <v>34.39880529944417</v>
+        <v>38.33846277218295</v>
       </c>
       <c r="D20" t="n">
-        <v>1.232007588064246</v>
+        <v>1.408872826827549</v>
       </c>
       <c r="E20" t="n">
-        <v>11.59454076033721</v>
+        <v>12.12068787380794</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587024404529508</v>
+        <v>0.751735549585875</v>
       </c>
       <c r="G20" t="n">
-        <v>20.83025667749045</v>
+        <v>24.08066232528574</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10669295915841</v>
+        <v>37.51632425575743</v>
       </c>
       <c r="I20" t="n">
-        <v>1.127310162905291</v>
+        <v>1.509193822460232</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741890252830943</v>
+        <v>4.698347184911719</v>
       </c>
       <c r="K20" t="n">
-        <v>22.6085991587605</v>
+        <v>17.91417616136353</v>
       </c>
       <c r="L20" t="n">
-        <v>42.95503677283651</v>
+        <v>43.69708541723667</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96244123104118</v>
+        <v>99.94972435078314</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.68961831170235</v>
+        <v>79.50057779156634</v>
       </c>
       <c r="C21" t="n">
-        <v>37.69652638848522</v>
+        <v>35.98632278155642</v>
       </c>
       <c r="D21" t="n">
-        <v>1.232794348309731</v>
+        <v>1.312722152552057</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37551613577571</v>
+        <v>11.50321389118696</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591869479544335</v>
+        <v>0.7521321620816649</v>
       </c>
       <c r="G21" t="n">
-        <v>22.35310196430883</v>
+        <v>22.43724080739733</v>
       </c>
       <c r="H21" t="n">
-        <v>38.63993238082519</v>
+        <v>37.53611770972423</v>
       </c>
       <c r="I21" t="n">
-        <v>1.584168109813249</v>
+        <v>1.258325055613675</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74491842471521</v>
+        <v>4.700826013010406</v>
       </c>
       <c r="K21" t="n">
-        <v>17.31038168829765</v>
+        <v>20.49942220843369</v>
       </c>
       <c r="L21" t="n">
-        <v>44.94032001970282</v>
+        <v>43.472332959386</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9472280964857</v>
+        <v>99.9580779493761</v>
       </c>
     </row>
   </sheetData>
